--- a/config/union/daily_notice.xlsx
+++ b/config/union/daily_notice.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ギルド寄付</t>
+          <t>公会捐赠</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未完了ミッション</t>
+          <t>未完成任务</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>未受取パック</t>
+          <t>未领取包</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>訓練助力</t>
+          <t>训练帮助</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>未受取ギフト</t>
+          <t>未收到的礼物</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ギルドダンジョン</t>
+          <t>公会地牢</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ギルド戦参加</t>
+          <t>参加公会战</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>祈願可能</t>
+          <t>可以祈祷</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
